--- a/Luban/Config/Datas/Levels/L03/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L03/EnemyList.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10016844,10016848,10016846,10048490,10016847,10016849,10016844,10016848,10016846,10048490,10016847,10016849,10016844,10016848,10016846,10048490,10016847,10016849,10016844,10016848,10016846,10016841,10016847,10016849,10016844,10016848,10016846,10016841,10016847,10016849,10016844,10016848,10016846,10016841,10016847,10016849,10016844,10016848,10016846,10016841,10016847,10016849,10016844,10016848,10016846,10048491,10016847,10016849,10016844,10016848,10016846,10048491,10016851,10016849,10016844,10016848,10016850,10048491,10016851,10016849,10016844,10016848,10016850,10048491,10016851,10016849,10016844,10016848,10016850,10016842,10016851,10016849,10016844,10016848,10016850,10016842,10016851,10016849,10016844,10016848,10016850,10016842,10016851,10016849,10016844,10016848,10016850,10016843,10016851,10016849,10016844,10016848,10016850,10016843,10016852,10016844,10016848,10016850,10016843,10016852,10016844,10016848,10016850,10016843,10016852,10016844,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016848,10016848,10016848,10016848</t>
+          <t>10016844,10048490,10016846,10048490,10016847,10016849,10016844,10048490,10016846,10048490,10016847,10016849,10016844,10048490,10016846,10048490,10016847,10016849,10016844,10016841,10016846,10016841,10016847,10016849,10016844,10016841,10016846,10016841,10016847,10016849,10016844,10016841,10016846,10016841,10016847,10016849,10016844,10016841,10016846,10016841,10016847,10016849,10016844,10048491,10016846,10048491,10016847,10016849,10016844,10048491,10016846,10048491,10016851,10016849,10016844,10048491,10016850,10048491,10016851,10016849,10016844,10048491,10016850,10048491,10016851,10016849,10016844,10016842,10016850,10016842,10016851,10016849,10016844,10016842,10016850,10016842,10016851,10016849,10016844,10016842,10016850,10016842,10016851,10016849,10016844,10016843,10016850,10016843,10016851,10016849,10016844,10016843,10016850,10016843,10016852,10016844,10016843,10016850,10016843,10016852,10016844,10016843,10016850,10016843,10016852,10016844,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016852,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016845,10016848,10016848,10016848,10016848,10016848</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L3 W21/25; N=153; EHP=15907.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x19,fast:30x9,medium:83x8,swarm:84x42,heavy:88x15,fast:98x9,medium:108x7,medium:123x7</t>
+          <t>L3 W21/25; N=153; EHP=26888.855482; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x9,fast:98x9,heavy:88x15,medium:83x8,medium:108x7,medium:123x7,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10016856,10016860,10016858,10048492,10016859,10016861,10016856,10016860,10016858,10048492,10016859,10016861,10016856,10016860,10016858,10048492,10016859,10016861,10016856,10016860,10016858,10048492,10016859,10016861,10016856,10016860,10016858,10016853,10016859,10016861,10016856,10016860,10016858,10016853,10016859,10016861,10016856,10016860,10016858,10016853,10016859,10016861,10016856,10016860,10016858,10048493,10016863,10016861,10016856,10016860,10016858,10048493,10016863,10016861,10016856,10016860,10016862,10048493,10016863,10016861,10016856,10016860,10016862,10048493,10016863,10016861,10016856,10016860,10016862,10016854,10016863,10016861,10016856,10016860,10016862,10016854,10016863,10016861,10016856,10016860,10016862,10016854,10016863,10016861,10016856,10016860,10016862,10016854,10016863,10016861,10016856,10016860,10016862,10016855,10016864,10016856,10016860,10016862,10016855,10016864,10016856,10016860,10016862,10016855,10016864,10016856,10016860,10016862,10016855,10016864,10016856,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016860,10016860,10016860,10016860,10016860</t>
+          <t>10016856,10048492,10016858,10048492,10016859,10016861,10016856,10048492,10016858,10048492,10016859,10016861,10016856,10048492,10016858,10048492,10016859,10016861,10016856,10048492,10016858,10048492,10016859,10016861,10016856,10016853,10016858,10016853,10016859,10016861,10016856,10016853,10016858,10016853,10016859,10016861,10016856,10016853,10016858,10016853,10016859,10016861,10016856,10048493,10016858,10048493,10016863,10016861,10016856,10048493,10016858,10048493,10016863,10016861,10016856,10048493,10016862,10048493,10016863,10016861,10016856,10048493,10016862,10048493,10016863,10016861,10016856,10016854,10016862,10016854,10016863,10016861,10016856,10016854,10016862,10016854,10016863,10016861,10016856,10016854,10016862,10016854,10016863,10016861,10016856,10016854,10016862,10016854,10016863,10016861,10016856,10016855,10016862,10016855,10016864,10016856,10016855,10016862,10016855,10016864,10016856,10016855,10016862,10016855,10016864,10016856,10016855,10016862,10016855,10016864,10016856,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016864,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016857,10016860,10016860,10016860,10016860,10016860,10016860</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L3 W22/25; N=159; EHP=16226.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x9,medium:83x7,swarm:84x44,heavy:88x15,fast:98x10,medium:108x8,medium:123x8</t>
+          <t>L3 W22/25; N=159; EHP=27434.691382; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x9,fast:98x10,heavy:88x15,medium:83x7,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10016868,10016872,10016870,10048494,10016871,10016873,10016868,10016872,10016870,10048494,10016871,10016873,10016868,10016872,10016870,10048494,10016871,10016873,10016868,10016872,10016870,10048494,10016871,10016873,10016868,10016872,10016870,10016865,10016871,10016873,10016868,10016872,10016870,10016865,10016871,10016873,10016868,10016872,10016870,10016865,10016871,10016873,10016868,10016872,10016870,10016865,10016871,10016873,10016868,10016872,10016870,10048495,10016875,10016873,10016868,10016872,10016870,10048495,10016875,10016873,10016868,10016872,10016874,10048495,10016875,10016873,10016868,10016872,10016874,10048495,10016875,10016873,10016868,10016872,10016874,10016866,10016875,10016873,10016868,10016872,10016874,10016866,10016875,10016873,10016868,10016872,10016874,10016866,10016875,10016873,10016868,10016872,10016874,10016866,10016875,10016873,10016868,10016872,10016874,10016867,10016876,10016868,10016872,10016874,10016867,10016876,10016868,10016872,10016874,10016867,10016876,10016868,10016872,10016867,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016872,10016872,10016872,10016872,10016872,10016872</t>
+          <t>10016868,10048494,10016870,10048494,10016871,10016873,10016868,10048494,10016870,10048494,10016871,10016873,10016868,10048494,10016870,10048494,10016871,10016873,10016868,10048494,10016870,10048494,10016871,10016873,10016868,10016865,10016870,10016865,10016871,10016873,10016868,10016865,10016870,10016865,10016871,10016873,10016868,10016865,10016870,10016865,10016871,10016873,10016868,10016865,10016870,10016865,10016871,10016873,10016868,10048495,10016870,10048495,10016875,10016873,10016868,10048495,10016870,10048495,10016875,10016873,10016868,10048495,10016874,10048495,10016875,10016873,10016868,10048495,10016874,10048495,10016875,10016873,10016868,10016866,10016874,10016866,10016875,10016873,10016868,10016866,10016874,10016866,10016875,10016873,10016868,10016866,10016874,10016866,10016875,10016873,10016868,10016866,10016874,10016866,10016875,10016873,10016868,10016867,10016874,10016867,10016876,10016868,10016867,10016874,10016867,10016876,10016868,10016867,10016874,10016867,10016876,10016868,10016867,10016867,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016876,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016869,10016872,10016872,10016872,10016872,10016872,10016872,10016872</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L3 W23/25; N=165; EHP=16551.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x10,medium:83x8,swarm:84x46,heavy:88x16,fast:98x9,medium:108x8,medium:123x8</t>
+          <t>L3 W23/25; N=165; EHP=27987.940066; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x9,heavy:88x16,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10016880,10016884,10016882,10048496,10016883,10016885,10016880,10016884,10016882,10048496,10016883,10016885,10016880,10016884,10016882,10048496,10016883,10016885,10016880,10016884,10016882,10048496,10016883,10016885,10016880,10016884,10016882,10048496,10016883,10016885,10016880,10016884,10016882,10016877,10016883,10016885,10016880,10016884,10016882,10016877,10016883,10016885,10016880,10016884,10016882,10016877,10016883,10016885,10016880,10016884,10016882,10016877,10016883,10016885,10016880,10016884,10016882,10048497,10016887,10016885,10016880,10016884,10016886,10048497,10016887,10016885,10016880,10016884,10016886,10048497,10016887,10016885,10016880,10016884,10016886,10048497,10016887,10016885,10016880,10016884,10016886,10016878,10016887,10016885,10016880,10016884,10016886,10016878,10016887,10016885,10016880,10016884,10016886,10016878,10016887,10016885,10016880,10016884,10016886,10016878,10016887,10016885,10016880,10016884,10016886,10016879,10016888,10016880,10016884,10016886,10016879,10016888,10016880,10016884,10016886,10016879,10016888,10016880,10016884,10016879,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016884,10016884,10016884,10016884,10016884,10016884</t>
+          <t>10016880,10048496,10016882,10048496,10016883,10016885,10016880,10048496,10016882,10048496,10016883,10016885,10016880,10048496,10016882,10048496,10016883,10016885,10016880,10048496,10016882,10048496,10016883,10016885,10016880,10048496,10016882,10048496,10016883,10016885,10016880,10016877,10016882,10016877,10016883,10016885,10016880,10016877,10016882,10016877,10016883,10016885,10016880,10016877,10016882,10016877,10016883,10016885,10016880,10016877,10016882,10016877,10016883,10016885,10016880,10048497,10016882,10048497,10016887,10016885,10016880,10048497,10016886,10048497,10016887,10016885,10016880,10048497,10016886,10048497,10016887,10016885,10016880,10048497,10016886,10048497,10016887,10016885,10016880,10016878,10016886,10016878,10016887,10016885,10016880,10016878,10016886,10016878,10016887,10016885,10016880,10016878,10016886,10016878,10016887,10016885,10016880,10016878,10016886,10016878,10016887,10016885,10016880,10016879,10016886,10016879,10016888,10016880,10016879,10016886,10016879,10016888,10016880,10016879,10016886,10016879,10016888,10016880,10016879,10016879,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016888,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016881,10016884,10016884,10016884,10016884,10016884,10016884,10016884</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L3 W24/25; N=171; EHP=17723.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x10,medium:83x9,swarm:84x47,heavy:88x17,fast:98x10,medium:108x8,medium:123x8</t>
+          <t>L3 W24/25; N=171; EHP=29973.120932; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x10,fast:98x10,heavy:88x17,medium:83x9,medium:108x8,medium:123x8,normal:17x21,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10016892,10016896,10016894,10048498,10016895,10016897,10016900,10016892,10016896,10016894,10048498,10016895,10016897,10016892,10016896,10016894,10048498,10016895,10016897,10016892,10016896,10016894,10048498,10016895,10016897,10016892,10016896,10016894,10016889,10016895,10016897,10016892,10016896,10016894,10016889,10016895,10016897,10016892,10016896,10016894,10016889,10016895,10016897,10016892,10016896,10016894,10016889,10016895,10016897,10016892,10016896,10016894,10048499,10016899,10016897,10016892,10016896,10016894,10048499,10016899,10016897,10016892,10016896,10016894,10048499,10016899,10016897,10016892,10016896,10016898,10048499,10016899,10016897,10016892,10016896,10016898,10016890,10016899,10016897,10016892,10016896,10016898,10016890,10016899,10016897,10016892,10016896,10016898,10016890,10016899,10016897,10016892,10016896,10016898,10016890,10016899,10016897,10016892,10016896,10016898,10016890,10016899,10016897,10016892,10016896,10016898,10016891,10016901,10016892,10016896,10016898,10016891,10016901,10016892,10016896,10016898,10016891,10016901,10016892,10016896,10016898,10016891,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016896,10016896,10016896,10016896,10016896,10016896,10016896</t>
+          <t>10016892,10048498,10016894,10048498,10016895,10016897,10016900,10016892,10048498,10016894,10048498,10016895,10016897,10016892,10048498,10016894,10048498,10016895,10016897,10016892,10048498,10016894,10048498,10016895,10016897,10016892,10016889,10016894,10016889,10016895,10016897,10016892,10016889,10016894,10016889,10016895,10016897,10016892,10016889,10016894,10016889,10016895,10016897,10016892,10016889,10016894,10016889,10016895,10016897,10016892,10048499,10016894,10048499,10016899,10016897,10016892,10048499,10016894,10048499,10016899,10016897,10016892,10048499,10016894,10048499,10016899,10016897,10016892,10048499,10016898,10048499,10016899,10016897,10016892,10016890,10016898,10016890,10016899,10016897,10016892,10016890,10016898,10016890,10016899,10016897,10016892,10016890,10016898,10016890,10016899,10016897,10016892,10016890,10016898,10016890,10016899,10016897,10016892,10016890,10016898,10016890,10016899,10016897,10016892,10016891,10016898,10016891,10016901,10016892,10016891,10016898,10016891,10016901,10016892,10016891,10016898,10016891,10016901,10016892,10016891,10016898,10016891,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016901,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016893,10016896,10016896,10016896,10016896,10016896,10016896,10016896,10016896</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L3 W25/25; N=177; EHP=35382.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x21,fast:30x11,medium:83x8,swarm:84x49,heavy:88x17,fast:98x10,medium:108x9,elite:123x1,medium:123x9</t>
+          <t>L3 W25/25; N=177; EHP=59802.085306; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x11,fast:98x10,heavy:88x17,medium:83x8,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L3 W1/25; N=33; EHP=184.404000; normal:17x16,normal:18x17</t>
+          <t>L3 W1/25; N=33; EHP=308.225460; normal:17x16,normal:18x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L3 W2/25; N=39; EHP=228.196597; normal:17x20,normal:18x19</t>
+          <t>L3 W2/25; N=39; EHP=381.423402; normal:17x20,normal:18x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3184136,3184673,3184019,3184136,3184673,3184091,3184136,3184673,3184099,3184136,3184673,3184107,3184136,3184673,3184115,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184136,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144</t>
+          <t>3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184136,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184144,3184136,3184136,3184136,3184136,3184136</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L3 W3/25; N=45; EHP=291.291264; air:2x1,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x14,normal:18x14,swarm:84x12</t>
+          <t>L3 W3/25; N=45; EHP=522.072880; normal:17x19,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3186136,3186673,3186019,3186136,3186673,3186019,3186136,3186673,3186091,3186136,3186673,3186099,3186136,3186673,3186107,3186136,3186673,3186115,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186136,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144</t>
+          <t>3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186136,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186144,3186136,3186136,3186136,3186136,3186136,3186136</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L3 W4/25; N=51; EHP=380.145493; air:2x2,air:11x1,air:12x1,air:13x1,air:14x1,normal:17x16,normal:18x15,swarm:84x14</t>
+          <t>L3 W4/25; N=51; EHP=684.392393; normal:17x22,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3188136,3188673,3188019,3188668,3188136,3188673,3188091,3188668,3188136,3188673,3188091,3188668,3188136,3188673,3188099,3188868,3188136,3188673,3188107,3188868,3188136,3188673,3188107,3188868,3188136,3188673,3188115,3188988,3188136,3188673,3188988,3188136,3188673,3188136,3188673,3188136,3188673,3188136,3188673,3188136,3188673,3188144,3188673,3188144,3188673,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144</t>
+          <t>3188136,3188019,3188019,3188668,3188136,3188091,3188091,3188668,3188136,3188091,3188091,3188668,3188136,3188099,3188099,3188868,3188136,3188107,3188107,3188868,3188136,3188107,3188107,3188868,3188136,3188115,3188115,3188988,3188136,3188673,3188988,3188136,3188673,3188136,3188673,3188136,3188673,3188136,3188673,3188136,3188673,3188144,3188673,3188144,3188673,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144,3188144</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L3 W5/25; N=57; EHP=731.776495; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x13,normal:18x14,medium:83x3,swarm:84x15,medium:108x3,medium:123x2</t>
+          <t>L3 W5/25; N=57; EHP=1239.145008; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x3,medium:108x3,medium:123x2,normal:17x13,normal:18x14,swarm:84x8 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3190136,3190673,3190242,3190019,3190668,3190136,3190673,3190242,3190091,3190668,3190136,3190673,3190242,3190091,3190668,3190136,3190673,3190242,3190099,3190868,3190136,3190673,3190242,3190099,3190868,3190136,3190673,3190242,3190107,3190868,3190136,3190673,3190242,3190115,3190988,3190136,3190673,3190115,3190988,3190136,3190673,3190988,3190136,3190673,3190136,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190144,3190144,3190144,3190144</t>
+          <t>3190136,3190019,3190242,3190019,3190668,3190136,3190091,3190242,3190091,3190668,3190136,3190091,3190242,3190091,3190668,3190136,3190099,3190242,3190099,3190868,3190136,3190099,3190242,3190099,3190868,3190136,3190107,3190242,3190107,3190868,3190136,3190115,3190242,3190115,3190988,3190136,3190115,3190115,3190988,3190136,3190673,3190988,3190136,3190673,3190136,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190673,3190144,3190144,3190144,3190144,3190144</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L3 W6/25; N=63; EHP=747.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x11,normal:18x11,fast:30x7,medium:83x3,swarm:84x17,medium:108x3,medium:123x3</t>
+          <t>L3 W6/25; N=63; EHP=1265.838530; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x7,medium:83x3,medium:108x3,medium:123x3,normal:17x11,normal:18x11,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3192136,3192673,3192242,3192019,3192668,3192136,3192673,3192242,3192019,3192668,3192136,3192673,3192242,3192091,3192668,3192136,3192673,3192242,3192099,3192868,3192136,3192673,3192242,3192099,3192868,3192136,3192673,3192242,3192107,3192868,3192136,3192673,3192242,3192115,3192988,3192136,3192673,3192242,3192115,3192988,3192136,3192673,3192988,3192136,3192673,3192988,3192136,3192673,3192136,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192144,3192144,3192144,3192144</t>
+          <t>3192136,3192019,3192242,3192019,3192668,3192136,3192019,3192242,3192019,3192668,3192136,3192091,3192242,3192091,3192668,3192136,3192099,3192242,3192099,3192868,3192136,3192099,3192242,3192099,3192868,3192136,3192107,3192242,3192107,3192868,3192136,3192115,3192242,3192115,3192988,3192136,3192115,3192242,3192115,3192988,3192136,3192673,3192988,3192136,3192673,3192988,3192136,3192673,3192136,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192673,3192144,3192144,3192144,3192144,3192144</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L3 W7/25; N=69; EHP=865.840483; air:2x2,air:11x1,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x12,fast:30x8,medium:83x3,swarm:84x19,medium:108x3,medium:123x4</t>
+          <t>L3 W7/25; N=69; EHP=1465.386265; air:2x4,air:11x2,air:12x4,air:13x2,air:14x4,fast:30x8,medium:83x3,medium:108x3,medium:123x4,normal:17x12,normal:18x12,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3194136,3194673,3194242,3194019,3194668,3194136,3194673,3194242,3194019,3194668,3194136,3194673,3194242,3194091,3194668,3194136,3194673,3194242,3194091,3194668,3194136,3194673,3194242,3194099,3194868,3194136,3194673,3194242,3194099,3194868,3194136,3194673,3194242,3194107,3194868,3194136,3194673,3194242,3194107,3194868,3194136,3194673,3194242,3194115,3194988,3194136,3194673,3194988,3194136,3194673,3194988,3194136,3194673,3194136,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194144,3194144,3194144</t>
+          <t>3194136,3194019,3194242,3194019,3194668,3194136,3194019,3194242,3194019,3194668,3194136,3194091,3194242,3194091,3194668,3194136,3194091,3194242,3194091,3194668,3194136,3194099,3194242,3194099,3194868,3194136,3194099,3194242,3194099,3194868,3194136,3194107,3194242,3194107,3194868,3194136,3194107,3194242,3194107,3194868,3194136,3194115,3194242,3194115,3194988,3194136,3194673,3194988,3194136,3194673,3194988,3194136,3194673,3194136,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194673,3194144,3194144,3194144,3194144</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L3 W8/25; N=75; EHP=1122.307890; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x13,normal:18x12,fast:30x9,medium:83x4,swarm:84x21,medium:108x4,medium:123x3</t>
+          <t>L3 W8/25; N=75; EHP=1900.352749; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,fast:30x9,medium:83x4,medium:108x4,medium:123x3,normal:17x13,normal:18x12,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3196136,3196673,3196242,3196019,3196668,3196136,3196673,3196242,3196019,3196668,3196136,3196673,3196242,3196091,3196668,3196136,3196673,3196242,3196091,3196668,3196136,3196673,3196242,3196099,3196868,3196136,3196673,3196242,3196099,3196868,3196136,3196673,3196242,3196107,3196868,3196136,3196673,3196242,3196107,3196868,3196136,3196673,3196242,3196115,3196988,3196136,3196673,3196115,3196988,3196136,3196673,3196988,3196136,3196673,3196988,3196136,3196673,3196136,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196144,3196144,3196144,3196144,3196144</t>
+          <t>3196136,3196019,3196242,3196019,3196668,3196136,3196019,3196242,3196019,3196668,3196136,3196091,3196242,3196091,3196668,3196136,3196091,3196242,3196091,3196668,3196136,3196099,3196242,3196099,3196868,3196136,3196099,3196242,3196099,3196868,3196136,3196107,3196242,3196107,3196868,3196136,3196107,3196242,3196107,3196868,3196136,3196115,3196242,3196115,3196988,3196136,3196115,3196115,3196988,3196136,3196673,3196988,3196136,3196673,3196988,3196136,3196673,3196136,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196673,3196144,3196144,3196144,3196144,3196144,3196144</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L3 W9/25; N=81; EHP=1437.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x9,medium:83x4,swarm:84x22,medium:108x4,medium:123x4</t>
+          <t>L3 W9/25; N=81; EHP=2433.989610; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x9,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3198136,3198673,3198242,3198019,3198668,3198136,3198673,3198242,3198019,3198668,3198136,3198673,3198242,3198091,3198668,3198136,3198673,3198242,3198091,3198668,3198136,3198673,3198242,3198099,3198868,3198136,3198673,3198242,3198099,3198868,3198136,3198673,3198242,3198107,3198868,3198136,3198673,3198242,3198107,3198868,3198136,3198673,3198242,3198115,3198988,3198136,3198673,3198242,3198115,3198988,3198136,3198673,3198988,3198136,3198673,3198988,3198136,3198673,3198988,3198136,3198673,3198136,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198144,3198144,3198144,3198144,3198144</t>
+          <t>3198136,3198019,3198242,3198019,3198668,3198136,3198019,3198242,3198019,3198668,3198136,3198091,3198242,3198091,3198668,3198136,3198091,3198242,3198091,3198668,3198136,3198099,3198242,3198099,3198868,3198136,3198099,3198242,3198099,3198868,3198136,3198107,3198242,3198107,3198868,3198136,3198107,3198242,3198107,3198868,3198136,3198115,3198242,3198115,3198988,3198136,3198115,3198242,3198115,3198988,3198136,3198673,3198988,3198136,3198673,3198988,3198136,3198673,3198988,3198136,3198673,3198136,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198673,3198144,3198144,3198144,3198144,3198144,3198144</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L3 W10/25; N=87; EHP=2654.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x10,medium:83x4,swarm:84x24,medium:108x4,medium:123x5</t>
+          <t>L3 W10/25; N=87; EHP=4491.047121; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x10,medium:83x4,medium:108x4,medium:123x5,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3200136,3200673,3200242,3200019,3200668,3200709,3200136,3200673,3200242,3200019,3200668,3200709,3200136,3200673,3200242,3200091,3200668,3200709,3200136,3200673,3200242,3200091,3200668,3200709,3200136,3200673,3200242,3200091,3200868,3200709,3200136,3200673,3200242,3200099,3200868,3200709,3200136,3200673,3200786,3200099,3200868,3200709,3200136,3200673,3200786,3200107,3200868,3200709,3200136,3200673,3200786,3200107,3200868,3200709,3200136,3200673,3200786,3200115,3200988,3200136,3200673,3200786,3200115,3200988,3200144,3200673,3200988,3200144,3200673,3200988,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200673,3200673,3200673</t>
+          <t>3200136,3200019,3200242,3200019,3200668,3200709,3200136,3200019,3200242,3200019,3200668,3200709,3200136,3200091,3200242,3200091,3200668,3200709,3200136,3200091,3200242,3200091,3200668,3200709,3200136,3200091,3200242,3200091,3200868,3200709,3200136,3200099,3200242,3200099,3200868,3200709,3200136,3200099,3200786,3200099,3200868,3200709,3200136,3200107,3200786,3200107,3200868,3200709,3200136,3200107,3200786,3200107,3200868,3200709,3200136,3200115,3200786,3200115,3200988,3200136,3200115,3200786,3200115,3200988,3200144,3200673,3200988,3200144,3200673,3200988,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200144,3200673,3200673,3200673,3200673</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L3 W11/25; N=93; EHP=2708.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x11,normal:18x12,fast:30x6,medium:83x4,swarm:84x26,heavy:88x9,fast:98x5,medium:108x5,medium:123x4</t>
+          <t>L3 W11/25; N=93; EHP=4578.146740; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x6,fast:98x5,heavy:88x9,medium:83x4,medium:108x5,medium:123x4,normal:17x11,normal:18x12,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3202136,3202673,3202242,3202019,3202668,3202709,3202136,3202673,3202242,3202019,3202668,3202709,3202136,3202673,3202242,3202091,3202668,3202709,3202136,3202673,3202242,3202091,3202668,3202709,3202136,3202673,3202242,3202099,3202668,3202709,3202136,3202673,3202786,3202099,3202868,3202709,3202136,3202673,3202786,3202099,3202868,3202709,3202136,3202673,3202786,3202107,3202868,3202709,3202136,3202673,3202786,3202107,3202868,3202709,3202136,3202673,3202786,3202115,3202988,3202136,3202673,3202786,3202115,3202988,3202136,3202673,3202115,3202988,3202136,3202673,3202988,3202144,3202673,3202988,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202673</t>
+          <t>3202136,3202019,3202242,3202019,3202668,3202709,3202136,3202019,3202242,3202019,3202668,3202709,3202136,3202091,3202242,3202091,3202668,3202709,3202136,3202091,3202242,3202091,3202668,3202709,3202136,3202099,3202242,3202099,3202668,3202709,3202136,3202099,3202786,3202099,3202868,3202709,3202136,3202099,3202786,3202099,3202868,3202709,3202136,3202107,3202786,3202107,3202868,3202709,3202136,3202107,3202786,3202107,3202868,3202709,3202136,3202115,3202786,3202115,3202988,3202136,3202115,3202786,3202115,3202988,3202136,3202115,3202115,3202988,3202136,3202673,3202988,3202144,3202673,3202988,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202144,3202673,3202673</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L3 W12/25; N=99; EHP=2803.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x5,medium:83x5,swarm:84x27,heavy:88x9,fast:98x6,medium:108x4,medium:123x5</t>
+          <t>L3 W12/25; N=99; EHP=4740.299156; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x5,fast:98x6,heavy:88x9,medium:83x5,medium:108x4,medium:123x5,normal:17x13,normal:18x13,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3204136,3204673,3204242,3204019,3204668,3204709,3204136,3204673,3204242,3204019,3204668,3204709,3204136,3204673,3204242,3204019,3204668,3204709,3204136,3204673,3204242,3204091,3204668,3204709,3204136,3204673,3204242,3204091,3204668,3204709,3204136,3204673,3204242,3204099,3204868,3204709,3204136,3204673,3204786,3204099,3204868,3204709,3204136,3204673,3204786,3204099,3204868,3204709,3204136,3204673,3204786,3204107,3204868,3204709,3204136,3204673,3204786,3204107,3204868,3204709,3204136,3204673,3204786,3204107,3204988,3204136,3204673,3204786,3204115,3204988,3204136,3204673,3204115,3204988,3204144,3204673,3204988,3204144,3204673,3204988,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204673,3204673,3204673</t>
+          <t>3204136,3204019,3204242,3204019,3204668,3204709,3204136,3204019,3204242,3204019,3204668,3204709,3204136,3204019,3204242,3204019,3204668,3204709,3204136,3204091,3204242,3204091,3204668,3204709,3204136,3204091,3204242,3204091,3204668,3204709,3204136,3204099,3204242,3204099,3204868,3204709,3204136,3204099,3204786,3204099,3204868,3204709,3204136,3204099,3204786,3204099,3204868,3204709,3204136,3204107,3204786,3204107,3204868,3204709,3204136,3204107,3204786,3204107,3204868,3204709,3204136,3204107,3204786,3204107,3204988,3204136,3204115,3204786,3204115,3204988,3204136,3204115,3204115,3204988,3204144,3204673,3204988,3204144,3204673,3204988,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204144,3204673,3204673,3204673,3204673</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L3 W13/25; N=105; EHP=3421.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x13,normal:18x13,fast:30x6,medium:83x5,swarm:84x29,heavy:88x10,fast:98x6,medium:108x5,medium:123x5</t>
+          <t>L3 W13/25; N=105; EHP=5786.668331; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x6,fast:98x6,heavy:88x10,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3206136,3206673,3206242,3206019,3206668,3206709,3206136,3206673,3206242,3206019,3206668,3206709,3206136,3206673,3206242,3206019,3206668,3206709,3206136,3206673,3206242,3206091,3206668,3206709,3206136,3206673,3206242,3206091,3206668,3206709,3206136,3206673,3206242,3206091,3206868,3206709,3206136,3206673,3206786,3206099,3206868,3206709,3206136,3206673,3206786,3206099,3206868,3206709,3206136,3206673,3206786,3206107,3206868,3206709,3206136,3206673,3206786,3206107,3206868,3206709,3206136,3206673,3206786,3206107,3206868,3206709,3206136,3206673,3206786,3206115,3206988,3206136,3206673,3206786,3206115,3206988,3206136,3206673,3206988,3206144,3206673,3206988,3206144,3206673,3206988,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206673,3206673,3206673,3206673</t>
+          <t>3206136,3206019,3206242,3206019,3206668,3206709,3206136,3206019,3206242,3206019,3206668,3206709,3206136,3206019,3206242,3206019,3206668,3206709,3206136,3206091,3206242,3206091,3206668,3206709,3206136,3206091,3206242,3206091,3206668,3206709,3206136,3206091,3206242,3206091,3206868,3206709,3206136,3206099,3206786,3206099,3206868,3206709,3206136,3206099,3206786,3206099,3206868,3206709,3206136,3206107,3206786,3206107,3206868,3206709,3206136,3206107,3206786,3206107,3206868,3206709,3206136,3206107,3206786,3206107,3206868,3206709,3206136,3206115,3206786,3206115,3206988,3206136,3206115,3206786,3206115,3206988,3206136,3206673,3206988,3206144,3206673,3206988,3206144,3206673,3206988,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206144,3206673,3206673,3206673,3206673,3206673</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L3 W14/25; N=111; EHP=4130.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x14,normal:18x13,fast:30x6,medium:83x5,swarm:84x31,heavy:88x11,fast:98x7,medium:108x6,medium:123x5</t>
+          <t>L3 W14/25; N=111; EHP=6980.896113; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x6,fast:98x7,heavy:88x11,medium:83x5,medium:108x6,medium:123x5,normal:17x14,normal:18x13,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3208136,3208673,3208242,3208019,3208668,3208709,3208136,3208673,3208242,3208019,3208668,3208709,3208136,3208673,3208242,3208091,3208668,3208709,3208136,3208673,3208242,3208091,3208668,3208709,3208136,3208673,3208242,3208091,3208668,3208709,3208136,3208673,3208242,3208099,3208668,3208709,3208136,3208673,3208242,3208099,3208868,3208709,3208136,3208673,3208786,3208099,3208868,3208709,3208136,3208673,3208786,3208107,3208868,3208709,3208136,3208673,3208786,3208107,3208868,3208709,3208136,3208673,3208786,3208107,3208868,3208709,3208136,3208673,3208786,3208115,3208988,3208136,3208673,3208786,3208115,3208988,3208136,3208673,3208786,3208115,3208988,3208144,3208673,3208988,3208144,3208673,3208988,3208144,3208673,3208988,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208673,3208673,3208673</t>
+          <t>3208136,3208019,3208242,3208019,3208668,3208709,3208136,3208019,3208242,3208019,3208668,3208709,3208136,3208091,3208242,3208091,3208668,3208709,3208136,3208091,3208242,3208091,3208668,3208709,3208136,3208091,3208242,3208091,3208668,3208709,3208136,3208099,3208242,3208099,3208668,3208709,3208136,3208099,3208242,3208099,3208868,3208709,3208136,3208099,3208786,3208099,3208868,3208709,3208136,3208107,3208786,3208107,3208868,3208709,3208136,3208107,3208786,3208107,3208868,3208709,3208136,3208107,3208786,3208107,3208868,3208709,3208136,3208115,3208786,3208115,3208988,3208136,3208115,3208786,3208115,3208988,3208136,3208115,3208786,3208115,3208988,3208144,3208673,3208988,3208144,3208673,3208988,3208144,3208673,3208988,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208144,3208673,3208673,3208673,3208673</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L3 W15/25; N=117; EHP=7208.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x7,medium:83x6,swarm:84x32,heavy:88x11,fast:98x7,medium:108x5,medium:123x6</t>
+          <t>L3 W15/25; N=117; EHP=12187.226848; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x7,fast:98x7,heavy:88x11,medium:83x6,medium:108x5,medium:123x6,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3210136,3210673,3210242,3210019,3210668,3210709,3210136,3210673,3210242,3210019,3210668,3210709,3210136,3210673,3210242,3210019,3210668,3210709,3210136,3210673,3210242,3210091,3210668,3210709,3210136,3210673,3210242,3210091,3210668,3210709,3210136,3210673,3210242,3210091,3210668,3210709,3210136,3210673,3210242,3210099,3210868,3210709,3210136,3210673,3210786,3210099,3210868,3210709,3210136,3210673,3210786,3210099,3210868,3210709,3210136,3210673,3210786,3210107,3210868,3210709,3210136,3210673,3210786,3210107,3210868,3210709,3210136,3210673,3210786,3210107,3210868,3210709,3210136,3210673,3210786,3210115,3210988,3210136,3210673,3210786,3210115,3210988,3210136,3210673,3210115,3210988,3210144,3210673,3210988,3210144,3210673,3210988,3210144,3210673,3210988,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210673,3210673,3210673,3210673</t>
+          <t>3210136,3210019,3210242,3210019,3210668,3210709,3210136,3210019,3210242,3210019,3210668,3210709,3210136,3210019,3210242,3210019,3210668,3210709,3210136,3210091,3210242,3210091,3210668,3210709,3210136,3210091,3210242,3210091,3210668,3210709,3210136,3210091,3210242,3210091,3210668,3210709,3210136,3210099,3210242,3210099,3210868,3210709,3210136,3210099,3210786,3210099,3210868,3210709,3210136,3210099,3210786,3210099,3210868,3210709,3210136,3210107,3210786,3210107,3210868,3210709,3210136,3210107,3210786,3210107,3210868,3210709,3210136,3210107,3210786,3210107,3210868,3210709,3210136,3210115,3210786,3210115,3210988,3210136,3210115,3210786,3210115,3210988,3210136,3210115,3210115,3210988,3210144,3210673,3210988,3210144,3210673,3210988,3210144,3210673,3210988,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210144,3210673,3210673,3210673,3210673,3210673</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L3 W16/25; N=123; EHP=7353.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x7,medium:83x6,swarm:84x34,heavy:88x12,fast:98x7,medium:108x6,medium:123x6</t>
+          <t>L3 W16/25; N=123; EHP=12434.616064; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x7,fast:98x7,heavy:88x12,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3212136,3212673,3212242,3212019,3212668,3212709,3212136,3212673,3212242,3212019,3212668,3212709,3212136,3212673,3212242,3212019,3212668,3212709,3212136,3212673,3212242,3212091,3212668,3212709,3212136,3212673,3212242,3212091,3212668,3212709,3212136,3212673,3212242,3212091,3212668,3212709,3212136,3212673,3212242,3212099,3212868,3212709,3212136,3212673,3212242,3212099,3212868,3212709,3212136,3212673,3212786,3212099,3212868,3212709,3212136,3212673,3212786,3212107,3212868,3212709,3212136,3212673,3212786,3212107,3212868,3212709,3212136,3212673,3212786,3212107,3212868,3212709,3212136,3212673,3212786,3212115,3212868,3212136,3212673,3212786,3212115,3212988,3212136,3212673,3212786,3212115,3212988,3212136,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212673,3212673,3212673,3212673</t>
+          <t>3212136,3212019,3212242,3212019,3212668,3212709,3212136,3212019,3212242,3212019,3212668,3212709,3212136,3212019,3212242,3212019,3212668,3212709,3212136,3212091,3212242,3212091,3212668,3212709,3212136,3212091,3212242,3212091,3212668,3212709,3212136,3212091,3212242,3212091,3212668,3212709,3212136,3212099,3212242,3212099,3212868,3212709,3212136,3212099,3212242,3212099,3212868,3212709,3212136,3212099,3212786,3212099,3212868,3212709,3212136,3212107,3212786,3212107,3212868,3212709,3212136,3212107,3212786,3212107,3212868,3212709,3212136,3212107,3212786,3212107,3212868,3212709,3212136,3212115,3212786,3212115,3212868,3212136,3212115,3212786,3212115,3212988,3212136,3212115,3212786,3212115,3212988,3212136,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212988,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212673,3212673,3212673,3212673</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L3 W17/25; N=129; EHP=7501.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x8,medium:83x6,swarm:84x36,heavy:88x12,fast:98x7,medium:108x7,medium:123x6</t>
+          <t>L3 W17/25; N=129; EHP=12678.451913; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x8,fast:98x7,heavy:88x12,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3214136,3214673,3214242,3214019,3214668,3214709,3214136,3214673,3214242,3214019,3214668,3214709,3214136,3214673,3214242,3214019,3214668,3214709,3214136,3214673,3214242,3214091,3214668,3214709,3214136,3214673,3214242,3214091,3214668,3214709,3214136,3214673,3214242,3214091,3214668,3214709,3214136,3214673,3214242,3214099,3214668,3214709,3214136,3214673,3214242,3214099,3214868,3214709,3214136,3214673,3214786,3214099,3214868,3214709,3214136,3214673,3214786,3214099,3214868,3214709,3214136,3214673,3214786,3214107,3214868,3214709,3214136,3214673,3214786,3214107,3214868,3214709,3214136,3214673,3214786,3214107,3214868,3214709,3214136,3214673,3214786,3214115,3214988,3214136,3214673,3214786,3214115,3214988,3214136,3214673,3214786,3214115,3214988,3214136,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214673,3214673,3214673,3214673</t>
+          <t>3214136,3214019,3214242,3214019,3214668,3214709,3214136,3214019,3214242,3214019,3214668,3214709,3214136,3214019,3214242,3214019,3214668,3214709,3214136,3214091,3214242,3214091,3214668,3214709,3214136,3214091,3214242,3214091,3214668,3214709,3214136,3214091,3214242,3214091,3214668,3214709,3214136,3214099,3214242,3214099,3214668,3214709,3214136,3214099,3214242,3214099,3214868,3214709,3214136,3214099,3214786,3214099,3214868,3214709,3214136,3214099,3214786,3214099,3214868,3214709,3214136,3214107,3214786,3214107,3214868,3214709,3214136,3214107,3214786,3214107,3214868,3214709,3214136,3214107,3214786,3214107,3214868,3214709,3214136,3214115,3214786,3214115,3214988,3214136,3214115,3214786,3214115,3214988,3214136,3214115,3214786,3214115,3214988,3214136,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214988,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214144,3214673,3214673,3214673,3214673,3214673</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L3 W18/25; N=135; EHP=8017.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x8,medium:83x7,swarm:84x37,heavy:88x13,fast:98x8,medium:108x6,medium:123x7</t>
+          <t>L3 W18/25; N=135; EHP=13552.816231; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x8,fast:98x8,heavy:88x13,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3216136,3216673,3216242,3216019,3216668,3216709,3216136,3216673,3216242,3216019,3216668,3216709,3216136,3216673,3216242,3216019,3216668,3216709,3216136,3216673,3216242,3216019,3216668,3216709,3216136,3216673,3216242,3216091,3216668,3216709,3216136,3216673,3216242,3216091,3216668,3216709,3216136,3216673,3216242,3216091,3216668,3216709,3216136,3216673,3216242,3216099,3216868,3216709,3216136,3216673,3216786,3216099,3216868,3216709,3216136,3216673,3216786,3216099,3216868,3216709,3216136,3216673,3216786,3216107,3216868,3216709,3216136,3216673,3216786,3216107,3216868,3216709,3216136,3216673,3216786,3216107,3216868,3216709,3216136,3216673,3216786,3216107,3216868,3216709,3216136,3216673,3216786,3216115,3216988,3216136,3216673,3216786,3216115,3216988,3216136,3216673,3216115,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216673,3216673,3216673,3216673,3216673</t>
+          <t>3216136,3216019,3216242,3216019,3216668,3216709,3216136,3216019,3216242,3216019,3216668,3216709,3216136,3216019,3216242,3216019,3216668,3216709,3216136,3216019,3216242,3216019,3216668,3216709,3216136,3216091,3216242,3216091,3216668,3216709,3216136,3216091,3216242,3216091,3216668,3216709,3216136,3216091,3216242,3216091,3216668,3216709,3216136,3216099,3216242,3216099,3216868,3216709,3216136,3216099,3216786,3216099,3216868,3216709,3216136,3216099,3216786,3216099,3216868,3216709,3216136,3216107,3216786,3216107,3216868,3216709,3216136,3216107,3216786,3216107,3216868,3216709,3216136,3216107,3216786,3216107,3216868,3216709,3216136,3216107,3216786,3216107,3216868,3216709,3216136,3216115,3216786,3216115,3216988,3216136,3216115,3216786,3216115,3216988,3216136,3216115,3216115,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216988,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216144,3216673,3216673,3216673,3216673,3216673,3216673</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L3 W19/25; N=141; EHP=9284.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x8,medium:83x7,swarm:84x39,heavy:88x14,fast:98x8,medium:108x7,medium:123x7</t>
+          <t>L3 W19/25; N=141; EHP=15697.249517; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x8,fast:98x8,heavy:88x14,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3218136,3218673,3218242,3218019,3218668,3218709,3218136,3218673,3218242,3218019,3218668,3218709,3218136,3218673,3218242,3218019,3218668,3218709,3218136,3218673,3218242,3218091,3218668,3218709,3218136,3218673,3218242,3218091,3218668,3218709,3218136,3218673,3218242,3218091,3218668,3218709,3218136,3218673,3218242,3218091,3218668,3218709,3218136,3218673,3218242,3218099,3218868,3218709,3218136,3218673,3218786,3218099,3218868,3218709,3218136,3218673,3218786,3218099,3218868,3218709,3218136,3218673,3218786,3218107,3218868,3218709,3218136,3218673,3218786,3218107,3218868,3218709,3218136,3218673,3218786,3218107,3218868,3218709,3218136,3218673,3218786,3218107,3218868,3218709,3218136,3218673,3218786,3218115,3218868,3218136,3218673,3218786,3218115,3218988,3218136,3218673,3218786,3218115,3218988,3218136,3218673,3218115,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218673,3218673,3218673,3218673,3218673,3218673</t>
+          <t>3218136,3218019,3218242,3218019,3218668,3218709,3218136,3218019,3218242,3218019,3218668,3218709,3218136,3218019,3218242,3218019,3218668,3218709,3218136,3218091,3218242,3218091,3218668,3218709,3218136,3218091,3218242,3218091,3218668,3218709,3218136,3218091,3218242,3218091,3218668,3218709,3218136,3218091,3218242,3218091,3218668,3218709,3218136,3218099,3218242,3218099,3218868,3218709,3218136,3218099,3218786,3218099,3218868,3218709,3218136,3218099,3218786,3218099,3218868,3218709,3218136,3218107,3218786,3218107,3218868,3218709,3218136,3218107,3218786,3218107,3218868,3218709,3218136,3218107,3218786,3218107,3218868,3218709,3218136,3218107,3218786,3218107,3218868,3218709,3218136,3218115,3218786,3218115,3218868,3218136,3218115,3218786,3218115,3218988,3218136,3218115,3218786,3218115,3218988,3218136,3218115,3218115,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218988,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673,3218673,3218673,3218673,3218673,3218673,3218673</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L3 W20/25; N=147; EHP=15595.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x17,fast:30x8,medium:83x7,swarm:84x41,heavy:88x14,fast:98x9,medium:108x8,medium:123x7</t>
+          <t>L3 W20/25; N=147; EHP=26374.422393; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x8,fast:98x9,heavy:88x14,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L03/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L03/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>136</v>
+        <v>310</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>276</v>
+        <v>340</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>199</v>
+        <v>340</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>178</v>
+        <v>300</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>157</v>
+        <v>300</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
